--- a/dist/downloads/model-documents/openbmb-minicpm-v-4.6.xlsx
+++ b/dist/downloads/model-documents/openbmb-minicpm-v-4.6.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="Re0ae1e8660764e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R04333dc9e64548db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R09b4a546c09f4e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R41c1df4567ff424e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,10 +624,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -690,7 +690,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC2" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD2" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -716,10 +716,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -782,7 +782,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC3" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD3" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -808,10 +808,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -874,7 +874,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC4" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD4" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -900,10 +900,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -966,7 +966,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC5" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD5" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -977,25 +977,25 @@
         <x:v>vision_config/layer_0</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1058,10 +1058,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC6" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -1084,10 +1084,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC7" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD7" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -1176,10 +1176,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1242,7 +1242,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC8" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD8" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -1268,10 +1268,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1334,7 +1334,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC9" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD9" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -1360,10 +1360,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1426,7 +1426,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC10" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD10" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -1452,10 +1452,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1518,7 +1518,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC11" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD11" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -1544,10 +1544,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC12" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD12" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -1636,10 +1636,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1702,7 +1702,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC13" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD13" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -1728,10 +1728,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1794,7 +1794,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -1820,10 +1820,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1886,7 +1886,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -1912,10 +1912,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -1978,7 +1978,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -2004,10 +2004,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I17" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2070,7 +2070,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD17" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -2096,10 +2096,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I18" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2162,7 +2162,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD18" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -2173,25 +2173,25 @@
         <x:v>vision_config/layer_1</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I19" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2254,10 +2254,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
@@ -2280,10 +2280,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2346,7 +2346,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -2372,10 +2372,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I21" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2438,7 +2438,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -2464,10 +2464,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I22" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2530,7 +2530,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -2556,10 +2556,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I23" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2622,7 +2622,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -2648,10 +2648,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I24" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2714,7 +2714,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -2740,10 +2740,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I25" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2806,7 +2806,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD25" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -2832,10 +2832,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2898,7 +2898,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD26" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -2924,10 +2924,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -2990,7 +2990,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -3016,10 +3016,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I28" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3082,7 +3082,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -3108,10 +3108,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I29" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3174,7 +3174,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -3200,10 +3200,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I30" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3266,7 +3266,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -3292,10 +3292,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I31" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3358,7 +3358,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -3369,25 +3369,25 @@
         <x:v>vision_config/layer_2</x:v>
       </x:c>
       <x:c r="B32" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I32" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3450,10 +3450,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" hidden="0" customHeight="1">
@@ -3476,10 +3476,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I33" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3542,7 +3542,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -3568,10 +3568,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I34" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3634,7 +3634,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -3660,10 +3660,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I35" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3726,7 +3726,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -3752,10 +3752,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3818,7 +3818,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -3844,10 +3844,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I37" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -3910,7 +3910,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -3936,10 +3936,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4002,7 +4002,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -4028,10 +4028,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4094,7 +4094,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -4120,10 +4120,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I40" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4186,7 +4186,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -4212,10 +4212,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I41" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4278,7 +4278,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -4304,10 +4304,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H42" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I42" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4370,7 +4370,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -4396,10 +4396,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H43" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I43" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4462,7 +4462,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -4488,10 +4488,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H44" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I44" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4554,7 +4554,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -4565,25 +4565,25 @@
         <x:v>vision_config/layer_3</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F45" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H45" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I45" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4646,10 +4646,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="24" hidden="0" customHeight="1">
@@ -4672,10 +4672,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I46" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4738,7 +4738,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -4764,10 +4764,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H47" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4830,7 +4830,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -4856,10 +4856,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H48" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I48" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -4922,7 +4922,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -4948,10 +4948,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H49" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I49" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5014,7 +5014,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -5040,10 +5040,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H50" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I50" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5106,7 +5106,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD50" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -5132,10 +5132,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H51" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5198,7 +5198,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -5224,10 +5224,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G52" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H52" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I52" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5290,7 +5290,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -5316,10 +5316,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G53" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H53" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I53" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5382,7 +5382,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -5408,10 +5408,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G54" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H54" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I54" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5474,7 +5474,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -5500,10 +5500,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H55" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I55" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5566,7 +5566,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -5592,10 +5592,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G56" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H56" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I56" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5658,7 +5658,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -5684,10 +5684,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G57" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H57" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I57" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5750,7 +5750,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -5761,25 +5761,25 @@
         <x:v>vision_config/layer_4</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D58" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F58" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G58" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H58" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I58" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5842,10 +5842,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" hidden="0" customHeight="1">
@@ -5868,10 +5868,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G59" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H59" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I59" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -5934,7 +5934,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -5960,10 +5960,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G60" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H60" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I60" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6026,7 +6026,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -6052,10 +6052,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G61" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H61" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I61" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6118,7 +6118,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD61" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -6144,10 +6144,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G62" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H62" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I62" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6210,7 +6210,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -6236,10 +6236,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G63" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H63" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I63" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6302,7 +6302,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC63" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD63" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -6328,10 +6328,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G64" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H64" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I64" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6394,7 +6394,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC64" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD64" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -6420,10 +6420,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G65" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H65" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I65" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6486,7 +6486,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -6512,10 +6512,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G66" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H66" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I66" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6578,7 +6578,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC66" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD66" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -6604,10 +6604,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G67" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H67" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I67" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6670,7 +6670,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC67" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD67" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -6696,10 +6696,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G68" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H68" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I68" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6762,7 +6762,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC68" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD68" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -6788,10 +6788,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G69" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H69" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I69" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6854,7 +6854,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC69" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD69" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -6880,10 +6880,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G70" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H70" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I70" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -6946,7 +6946,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC70" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD70" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -6957,25 +6957,25 @@
         <x:v>vision_config/layer_5</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D71" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F71" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G71" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H71" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I71" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7038,10 +7038,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC71" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD71" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="24" hidden="0" customHeight="1">
@@ -7064,10 +7064,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G72" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H72" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I72" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7130,7 +7130,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC72" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD72" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -7156,10 +7156,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G73" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H73" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I73" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7222,7 +7222,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC73" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD73" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -7248,10 +7248,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G74" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H74" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I74" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7314,7 +7314,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC74" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD74" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -7340,10 +7340,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G75" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H75" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I75" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7406,7 +7406,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC75" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD75" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -7432,10 +7432,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G76" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H76" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I76" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7498,7 +7498,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC76" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD76" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -7524,10 +7524,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G77" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H77" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I77" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7590,7 +7590,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC77" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD77" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -7616,10 +7616,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G78" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H78" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I78" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7682,7 +7682,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC78" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD78" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -7708,10 +7708,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G79" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H79" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I79" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7774,7 +7774,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC79" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD79" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -7800,10 +7800,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G80" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H80" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I80" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7866,7 +7866,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC80" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD80" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -7892,10 +7892,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G81" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H81" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I81" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -7958,7 +7958,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC81" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD81" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -7984,10 +7984,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G82" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H82" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I82" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8050,7 +8050,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC82" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD82" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -8076,10 +8076,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G83" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H83" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I83" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8142,7 +8142,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC83" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD83" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -8153,25 +8153,25 @@
         <x:v>vision_config/layer_6</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C84" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D84" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F84" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G84" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H84" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I84" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8234,10 +8234,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC84" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD84" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="24" hidden="0" customHeight="1">
@@ -8260,10 +8260,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G85" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H85" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I85" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8326,7 +8326,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC85" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD85" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -8352,10 +8352,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G86" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H86" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I86" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8418,7 +8418,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC86" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD86" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -8444,10 +8444,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G87" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H87" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I87" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8510,7 +8510,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC87" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD87" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -8536,10 +8536,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G88" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H88" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I88" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8602,7 +8602,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC88" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD88" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -8628,10 +8628,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G89" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H89" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I89" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8694,7 +8694,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC89" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD89" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -8720,10 +8720,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G90" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H90" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I90" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8786,7 +8786,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC90" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD90" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -8812,10 +8812,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G91" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H91" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I91" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8878,7 +8878,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC91" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD91" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -8904,10 +8904,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G92" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H92" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I92" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -8970,7 +8970,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC92" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD92" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -8996,10 +8996,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G93" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H93" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I93" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9062,7 +9062,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC93" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD93" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -9088,10 +9088,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G94" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H94" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I94" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9154,7 +9154,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC94" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD94" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -9180,10 +9180,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G95" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H95" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I95" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9246,7 +9246,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC95" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD95" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -9272,10 +9272,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G96" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H96" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I96" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9338,7 +9338,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC96" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD96" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -9349,25 +9349,25 @@
         <x:v>vision_config/layer_7</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C97" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D97" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F97" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G97" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H97" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I97" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9430,10 +9430,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC97" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD97" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="24" hidden="0" customHeight="1">
@@ -9456,10 +9456,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G98" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H98" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I98" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9522,7 +9522,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC98" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD98" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -9548,10 +9548,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G99" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H99" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I99" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9614,7 +9614,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC99" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD99" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -9640,10 +9640,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G100" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H100" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I100" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9706,7 +9706,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC100" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD100" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -9732,10 +9732,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G101" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H101" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I101" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9798,7 +9798,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC101" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD101" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -9824,10 +9824,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G102" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H102" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I102" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9890,7 +9890,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC102" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD102" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -9916,10 +9916,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G103" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H103" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I103" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -9982,7 +9982,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC103" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD103" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -10008,10 +10008,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G104" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H104" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I104" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10074,7 +10074,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC104" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD104" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -10100,10 +10100,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G105" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H105" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I105" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10166,7 +10166,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC105" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD105" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -10192,10 +10192,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G106" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H106" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I106" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10258,7 +10258,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC106" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD106" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -10284,10 +10284,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G107" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H107" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I107" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10350,7 +10350,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC107" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD107" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -10376,10 +10376,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G108" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H108" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I108" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10442,7 +10442,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC108" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD108" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -10468,10 +10468,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G109" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H109" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I109" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10534,7 +10534,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC109" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD109" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -10545,25 +10545,25 @@
         <x:v>vision_config/layer_8</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C110" s="11" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D110" s="11" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F110" s="11" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G110" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H110" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I110" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10626,10 +10626,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC110" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD110" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="24" hidden="0" customHeight="1">
@@ -10652,10 +10652,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G111" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H111" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I111" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10718,7 +10718,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC111" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD111" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -10744,10 +10744,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G112" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H112" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I112" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10810,7 +10810,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC112" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD112" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -10836,10 +10836,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G113" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H113" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I113" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10902,7 +10902,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC113" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD113" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -10928,10 +10928,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G114" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H114" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I114" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -10994,7 +10994,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC114" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD114" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -11020,10 +11020,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G115" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H115" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I115" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11086,7 +11086,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC115" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD115" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -11112,10 +11112,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G116" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H116" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I116" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11178,7 +11178,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC116" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD116" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -11204,10 +11204,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G117" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H117" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I117" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11270,7 +11270,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC117" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD117" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -11296,10 +11296,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G118" s="11" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H118" s="11" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I118" s="11" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11362,7 +11362,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC118" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD118" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -11388,10 +11388,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G119" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H119" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I119" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11454,7 +11454,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC119" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD119" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -11480,10 +11480,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G120" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H120" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I120" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11546,7 +11546,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC120" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD120" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -11572,10 +11572,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G121" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H121" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I121" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11638,7 +11638,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC121" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD121" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -11664,10 +11664,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G122" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H122" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I122" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11730,7 +11730,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC122" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD122" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -11741,25 +11741,25 @@
         <x:v>vision_config/layer_9</x:v>
       </x:c>
       <x:c r="B123" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C123" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D123" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E123" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F123" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G123" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H123" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I123" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11822,10 +11822,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC123" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD123" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
@@ -11848,10 +11848,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G124" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H124" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I124" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -11914,7 +11914,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC124" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD124" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -11940,10 +11940,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G125" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H125" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I125" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12006,7 +12006,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC125" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD125" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -12032,10 +12032,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G126" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H126" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I126" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12098,7 +12098,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC126" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD126" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -12124,10 +12124,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G127" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H127" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I127" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12190,7 +12190,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC127" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD127" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -12216,10 +12216,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G128" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H128" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I128" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12282,7 +12282,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC128" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD128" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -12308,10 +12308,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G129" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H129" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I129" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12374,7 +12374,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC129" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD129" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -12400,10 +12400,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G130" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H130" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I130" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12466,7 +12466,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC130" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD130" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -12492,10 +12492,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G131" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H131" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I131" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12558,7 +12558,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC131" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD131" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -12584,10 +12584,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G132" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H132" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I132" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12650,7 +12650,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC132" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD132" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -12676,10 +12676,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G133" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H133" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I133" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12742,7 +12742,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC133" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD133" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -12768,10 +12768,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G134" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H134" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I134" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12834,7 +12834,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC134" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD134" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -12860,10 +12860,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G135" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H135" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I135" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -12926,7 +12926,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC135" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD135" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -12937,25 +12937,25 @@
         <x:v>vision_config/layer_10</x:v>
       </x:c>
       <x:c r="B136" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C136" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D136" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E136" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F136" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G136" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H136" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I136" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13018,10 +13018,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC136" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD136" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="24" hidden="0" customHeight="1">
@@ -13044,10 +13044,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G137" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H137" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I137" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13110,7 +13110,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC137" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD137" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -13136,10 +13136,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G138" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H138" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I138" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13202,7 +13202,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC138" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD138" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -13228,10 +13228,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G139" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H139" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I139" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13294,7 +13294,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC139" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD139" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -13320,10 +13320,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G140" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H140" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I140" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13386,7 +13386,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC140" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD140" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -13412,10 +13412,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G141" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H141" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I141" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13478,7 +13478,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC141" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD141" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -13504,10 +13504,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G142" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H142" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I142" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13570,7 +13570,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC142" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD142" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -13596,10 +13596,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G143" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H143" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I143" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13662,7 +13662,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC143" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD143" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -13688,10 +13688,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G144" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H144" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I144" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13754,7 +13754,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC144" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD144" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -13780,10 +13780,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G145" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H145" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I145" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13846,7 +13846,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC145" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD145" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -13872,10 +13872,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G146" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H146" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I146" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -13938,7 +13938,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC146" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD146" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -13964,10 +13964,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G147" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H147" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I147" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14030,7 +14030,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC147" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD147" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -14056,10 +14056,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G148" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H148" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I148" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14122,7 +14122,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC148" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD148" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -14133,25 +14133,25 @@
         <x:v>vision_config/layer_11</x:v>
       </x:c>
       <x:c r="B149" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C149" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D149" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E149" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F149" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G149" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H149" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I149" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14214,10 +14214,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC149" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD149" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="24" hidden="0" customHeight="1">
@@ -14240,10 +14240,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G150" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H150" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I150" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14306,7 +14306,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC150" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD150" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -14332,10 +14332,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G151" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H151" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I151" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14398,7 +14398,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC151" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD151" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -14424,10 +14424,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G152" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H152" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I152" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14490,7 +14490,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC152" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD152" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -14516,10 +14516,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G153" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H153" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I153" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14582,7 +14582,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC153" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD153" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -14608,10 +14608,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G154" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H154" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I154" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14674,7 +14674,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC154" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD154" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -14700,10 +14700,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G155" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H155" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I155" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14766,7 +14766,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC155" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD155" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -14792,10 +14792,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G156" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H156" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I156" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14858,7 +14858,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC156" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD156" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -14884,10 +14884,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G157" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H157" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I157" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -14950,7 +14950,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC157" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD157" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -14976,10 +14976,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G158" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H158" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I158" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15042,7 +15042,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC158" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD158" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -15068,10 +15068,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G159" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H159" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I159" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15134,7 +15134,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC159" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD159" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -15160,10 +15160,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G160" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H160" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I160" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15226,7 +15226,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC160" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD160" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -15252,10 +15252,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G161" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H161" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I161" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15318,7 +15318,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC161" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD161" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -15329,25 +15329,25 @@
         <x:v>vision_config/layer_12</x:v>
       </x:c>
       <x:c r="B162" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C162" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D162" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E162" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F162" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G162" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H162" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I162" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15410,10 +15410,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC162" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD162" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="24" hidden="0" customHeight="1">
@@ -15436,10 +15436,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G163" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H163" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I163" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15502,7 +15502,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC163" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD163" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -15528,10 +15528,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G164" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H164" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I164" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15594,7 +15594,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC164" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD164" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -15620,10 +15620,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G165" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H165" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I165" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15686,7 +15686,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC165" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD165" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -15712,10 +15712,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G166" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H166" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I166" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15778,7 +15778,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC166" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD166" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -15804,10 +15804,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G167" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H167" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I167" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15870,7 +15870,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC167" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD167" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -15896,10 +15896,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G168" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H168" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I168" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -15962,7 +15962,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC168" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD168" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -15988,10 +15988,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G169" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H169" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I169" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16054,7 +16054,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC169" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD169" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -16080,10 +16080,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G170" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H170" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I170" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16146,7 +16146,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC170" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD170" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -16172,10 +16172,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G171" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H171" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I171" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16238,7 +16238,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC171" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD171" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -16264,10 +16264,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G172" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H172" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I172" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16330,7 +16330,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC172" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD172" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -16356,10 +16356,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G173" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H173" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I173" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16422,7 +16422,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC173" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD173" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -16448,10 +16448,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G174" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H174" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I174" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16514,7 +16514,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC174" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD174" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -16525,25 +16525,25 @@
         <x:v>vision_config/layer_13</x:v>
       </x:c>
       <x:c r="B175" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C175" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D175" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E175" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F175" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G175" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H175" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I175" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16606,10 +16606,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC175" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD175" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="24" hidden="0" customHeight="1">
@@ -16632,10 +16632,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G176" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H176" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I176" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16698,7 +16698,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC176" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD176" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -16724,10 +16724,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G177" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H177" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I177" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16790,7 +16790,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC177" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD177" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -16816,10 +16816,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G178" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H178" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I178" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16882,7 +16882,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC178" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD178" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -16908,10 +16908,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G179" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H179" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I179" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -16974,7 +16974,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC179" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD179" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -17000,10 +17000,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G180" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H180" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I180" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17066,7 +17066,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC180" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD180" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -17092,10 +17092,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G181" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H181" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I181" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17158,7 +17158,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC181" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD181" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -17184,10 +17184,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G182" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H182" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I182" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17250,7 +17250,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC182" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD182" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -17276,10 +17276,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G183" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H183" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I183" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17342,7 +17342,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC183" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD183" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -17368,10 +17368,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G184" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H184" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I184" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17434,7 +17434,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC184" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD184" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -17460,10 +17460,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G185" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H185" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I185" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17526,7 +17526,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC185" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD185" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -17552,10 +17552,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G186" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H186" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I186" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17618,7 +17618,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC186" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD186" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -17644,10 +17644,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G187" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H187" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I187" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17710,7 +17710,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC187" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD187" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -17721,25 +17721,25 @@
         <x:v>vision_config/layer_14</x:v>
       </x:c>
       <x:c r="B188" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C188" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D188" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F188" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G188" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H188" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I188" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17802,10 +17802,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC188" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD188" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="24" hidden="0" customHeight="1">
@@ -17828,10 +17828,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G189" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H189" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I189" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17894,7 +17894,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC189" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD189" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -17920,10 +17920,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G190" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H190" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I190" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -17986,7 +17986,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC190" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD190" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -18012,10 +18012,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G191" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H191" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I191" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18078,7 +18078,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC191" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD191" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -18104,10 +18104,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G192" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H192" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I192" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18170,7 +18170,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC192" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD192" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -18196,10 +18196,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G193" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H193" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I193" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18262,7 +18262,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC193" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD193" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -18288,10 +18288,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G194" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H194" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I194" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18354,7 +18354,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC194" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD194" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -18380,10 +18380,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G195" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H195" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I195" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18446,7 +18446,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC195" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD195" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -18472,10 +18472,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G196" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H196" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I196" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18538,7 +18538,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC196" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD196" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -18564,10 +18564,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G197" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H197" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I197" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18630,7 +18630,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC197" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD197" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -18656,10 +18656,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G198" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H198" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I198" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18722,7 +18722,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC198" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD198" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -18748,10 +18748,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G199" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H199" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I199" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18814,7 +18814,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC199" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD199" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -18840,10 +18840,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G200" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H200" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I200" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18906,7 +18906,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC200" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD200" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -18917,25 +18917,25 @@
         <x:v>vision_config/layer_15</x:v>
       </x:c>
       <x:c r="B201" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C201" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D201" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E201" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F201" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G201" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H201" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I201" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -18998,10 +18998,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC201" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD201" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="24" hidden="0" customHeight="1">
@@ -19024,10 +19024,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G202" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H202" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I202" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19090,7 +19090,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC202" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD202" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -19116,10 +19116,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G203" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H203" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I203" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19182,7 +19182,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC203" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD203" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -19208,10 +19208,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G204" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H204" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I204" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19274,7 +19274,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC204" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD204" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -19300,10 +19300,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G205" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H205" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I205" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19366,7 +19366,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC205" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD205" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -19392,10 +19392,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G206" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H206" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I206" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19458,7 +19458,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC206" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD206" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -19484,10 +19484,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G207" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H207" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I207" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19550,7 +19550,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC207" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD207" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -19576,10 +19576,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G208" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H208" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I208" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19642,7 +19642,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC208" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD208" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -19668,10 +19668,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G209" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H209" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I209" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19734,7 +19734,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC209" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD209" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -19760,10 +19760,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G210" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H210" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I210" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19826,7 +19826,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC210" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD210" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -19852,10 +19852,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G211" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H211" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I211" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -19918,7 +19918,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC211" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD211" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -19944,10 +19944,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G212" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H212" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I212" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20010,7 +20010,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC212" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD212" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -20036,10 +20036,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G213" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H213" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I213" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20102,7 +20102,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC213" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD213" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -20113,25 +20113,25 @@
         <x:v>vision_config/layer_16</x:v>
       </x:c>
       <x:c r="B214" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C214" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D214" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F214" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G214" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H214" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I214" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20194,10 +20194,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC214" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD214" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="24" hidden="0" customHeight="1">
@@ -20220,10 +20220,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G215" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H215" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I215" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20286,7 +20286,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC215" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD215" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -20312,10 +20312,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G216" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H216" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I216" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20378,7 +20378,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC216" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD216" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -20404,10 +20404,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G217" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H217" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I217" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20470,7 +20470,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC217" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD217" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -20496,10 +20496,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G218" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H218" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I218" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20562,7 +20562,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC218" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD218" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -20588,10 +20588,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G219" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H219" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I219" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20654,7 +20654,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC219" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD219" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -20680,10 +20680,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G220" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H220" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I220" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20746,7 +20746,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC220" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD220" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -20772,10 +20772,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G221" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H221" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I221" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20838,7 +20838,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC221" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD221" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -20864,10 +20864,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G222" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H222" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I222" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -20930,7 +20930,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC222" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD222" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -20956,10 +20956,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G223" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H223" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I223" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21022,7 +21022,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC223" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD223" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -21048,10 +21048,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G224" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H224" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I224" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21114,7 +21114,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC224" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD224" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -21140,10 +21140,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G225" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H225" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I225" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21206,7 +21206,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC225" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD225" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -21232,10 +21232,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G226" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H226" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I226" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21298,7 +21298,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC226" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD226" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -21309,25 +21309,25 @@
         <x:v>vision_config/layer_17</x:v>
       </x:c>
       <x:c r="B227" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C227" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D227" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E227" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F227" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G227" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H227" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I227" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21390,10 +21390,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC227" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD227" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="24" hidden="0" customHeight="1">
@@ -21416,10 +21416,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G228" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H228" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I228" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21482,7 +21482,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC228" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD228" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -21508,10 +21508,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G229" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H229" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I229" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21574,7 +21574,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC229" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD229" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -21600,10 +21600,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G230" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H230" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I230" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21666,7 +21666,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC230" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD230" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -21692,10 +21692,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G231" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H231" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I231" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21758,7 +21758,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC231" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD231" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -21784,10 +21784,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G232" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H232" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I232" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21850,7 +21850,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC232" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD232" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -21876,10 +21876,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G233" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H233" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I233" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -21942,7 +21942,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC233" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD233" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -21968,10 +21968,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G234" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H234" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I234" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22034,7 +22034,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC234" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD234" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -22060,10 +22060,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G235" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H235" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I235" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22126,7 +22126,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC235" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD235" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -22152,10 +22152,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G236" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H236" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I236" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22218,7 +22218,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC236" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD236" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -22244,10 +22244,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G237" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H237" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I237" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22310,7 +22310,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC237" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD237" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -22336,10 +22336,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G238" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H238" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I238" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22402,7 +22402,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC238" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD238" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -22428,10 +22428,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G239" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H239" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I239" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22494,7 +22494,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC239" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD239" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -22505,25 +22505,25 @@
         <x:v>vision_config/layer_18</x:v>
       </x:c>
       <x:c r="B240" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C240" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D240" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E240" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F240" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G240" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H240" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I240" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22586,10 +22586,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC240" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD240" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="24" hidden="0" customHeight="1">
@@ -22612,10 +22612,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G241" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H241" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I241" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22678,7 +22678,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC241" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD241" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -22704,10 +22704,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G242" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H242" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I242" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22770,7 +22770,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC242" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD242" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -22796,10 +22796,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G243" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H243" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I243" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22862,7 +22862,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC243" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD243" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -22888,10 +22888,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G244" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H244" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I244" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -22954,7 +22954,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC244" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD244" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -22980,10 +22980,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G245" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H245" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I245" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23046,7 +23046,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC245" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD245" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -23072,10 +23072,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G246" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H246" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I246" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23138,7 +23138,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC246" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD246" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -23164,10 +23164,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G247" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H247" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I247" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23230,7 +23230,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC247" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD247" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -23256,10 +23256,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G248" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H248" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I248" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23322,7 +23322,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC248" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD248" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -23348,10 +23348,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G249" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H249" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I249" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23414,7 +23414,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC249" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD249" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -23440,10 +23440,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G250" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H250" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I250" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23506,7 +23506,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC250" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD250" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -23532,10 +23532,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G251" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H251" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I251" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23598,7 +23598,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC251" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD251" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -23624,10 +23624,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G252" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H252" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I252" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23690,7 +23690,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC252" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD252" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -23701,25 +23701,25 @@
         <x:v>vision_config/layer_19</x:v>
       </x:c>
       <x:c r="B253" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C253" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D253" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E253" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F253" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G253" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H253" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I253" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23782,10 +23782,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC253" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD253" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="24" hidden="0" customHeight="1">
@@ -23808,10 +23808,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G254" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H254" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I254" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23874,7 +23874,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC254" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD254" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -23900,10 +23900,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G255" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H255" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I255" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -23966,7 +23966,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC255" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD255" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -23992,10 +23992,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G256" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H256" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I256" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24058,7 +24058,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC256" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD256" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -24084,10 +24084,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G257" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H257" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I257" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24150,7 +24150,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC257" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD257" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -24176,10 +24176,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G258" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H258" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I258" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24242,7 +24242,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC258" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD258" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -24268,10 +24268,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G259" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H259" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I259" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24334,7 +24334,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC259" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD259" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -24360,10 +24360,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G260" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H260" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I260" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24426,7 +24426,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC260" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD260" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -24452,10 +24452,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G261" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H261" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I261" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24518,7 +24518,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC261" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD261" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -24544,10 +24544,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G262" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H262" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I262" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24610,7 +24610,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC262" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD262" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -24636,10 +24636,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G263" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H263" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I263" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24702,7 +24702,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC263" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD263" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -24728,10 +24728,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G264" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H264" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I264" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24794,7 +24794,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC264" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD264" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -24820,10 +24820,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G265" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H265" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I265" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24886,7 +24886,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC265" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD265" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -24897,25 +24897,25 @@
         <x:v>vision_config/layer_20</x:v>
       </x:c>
       <x:c r="B266" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C266" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D266" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E266" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F266" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G266" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H266" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I266" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -24978,10 +24978,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC266" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD266" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="24" hidden="0" customHeight="1">
@@ -25004,10 +25004,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G267" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H267" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I267" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25070,7 +25070,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC267" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD267" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -25096,10 +25096,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G268" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H268" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I268" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25162,7 +25162,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC268" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD268" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -25188,10 +25188,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G269" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H269" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I269" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25254,7 +25254,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC269" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD269" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -25280,10 +25280,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G270" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H270" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I270" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25346,7 +25346,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC270" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD270" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -25372,10 +25372,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G271" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H271" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I271" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25438,7 +25438,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC271" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD271" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -25464,10 +25464,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G272" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H272" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I272" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25530,7 +25530,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC272" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD272" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -25556,10 +25556,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G273" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H273" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I273" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25622,7 +25622,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC273" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD273" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -25648,10 +25648,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G274" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H274" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I274" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25714,7 +25714,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC274" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD274" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -25740,10 +25740,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G275" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H275" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I275" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25806,7 +25806,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC275" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD275" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -25832,10 +25832,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G276" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H276" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I276" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25898,7 +25898,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC276" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD276" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -25924,10 +25924,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G277" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H277" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I277" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -25990,7 +25990,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC277" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD277" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -26016,10 +26016,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G278" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H278" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I278" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26082,7 +26082,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC278" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD278" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -26093,25 +26093,25 @@
         <x:v>vision_config/layer_21</x:v>
       </x:c>
       <x:c r="B279" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C279" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D279" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E279" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F279" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G279" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H279" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I279" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26174,10 +26174,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC279" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD279" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="24" hidden="0" customHeight="1">
@@ -26200,10 +26200,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G280" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H280" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I280" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26266,7 +26266,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC280" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD280" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -26292,10 +26292,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G281" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H281" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I281" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26358,7 +26358,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC281" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD281" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -26384,10 +26384,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G282" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H282" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I282" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26450,7 +26450,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC282" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD282" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -26476,10 +26476,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G283" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H283" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I283" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26542,7 +26542,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC283" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD283" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -26568,10 +26568,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G284" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H284" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I284" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26634,7 +26634,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC284" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD284" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -26660,10 +26660,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G285" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H285" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I285" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26726,7 +26726,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC285" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD285" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -26752,10 +26752,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G286" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H286" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I286" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26818,7 +26818,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC286" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD286" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -26844,10 +26844,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G287" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H287" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I287" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -26910,7 +26910,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC287" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD287" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -26936,10 +26936,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G288" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H288" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I288" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27002,7 +27002,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC288" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD288" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -27028,10 +27028,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G289" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H289" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I289" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27094,7 +27094,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC289" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD289" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -27120,10 +27120,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G290" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H290" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I290" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27186,7 +27186,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC290" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD290" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -27212,10 +27212,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G291" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H291" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I291" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27278,7 +27278,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC291" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD291" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -27289,25 +27289,25 @@
         <x:v>vision_config/layer_22</x:v>
       </x:c>
       <x:c r="B292" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C292" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D292" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E292" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F292" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G292" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H292" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I292" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27370,10 +27370,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC292" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD292" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="24" hidden="0" customHeight="1">
@@ -27396,10 +27396,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G293" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H293" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I293" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27462,7 +27462,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC293" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD293" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -27488,10 +27488,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G294" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H294" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I294" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27554,7 +27554,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC294" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD294" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -27580,10 +27580,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G295" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H295" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I295" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27646,7 +27646,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC295" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD295" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -27672,10 +27672,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G296" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H296" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I296" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27738,7 +27738,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC296" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD296" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -27764,10 +27764,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G297" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H297" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I297" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27830,7 +27830,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC297" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD297" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -27856,10 +27856,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G298" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H298" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I298" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -27922,7 +27922,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC298" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD298" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -27948,10 +27948,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G299" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H299" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I299" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28014,7 +28014,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC299" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD299" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -28040,10 +28040,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G300" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H300" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I300" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28106,7 +28106,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC300" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD300" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -28132,10 +28132,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G301" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H301" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I301" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28198,7 +28198,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC301" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD301" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -28224,10 +28224,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G302" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H302" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I302" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28290,7 +28290,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC302" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD302" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -28316,10 +28316,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G303" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H303" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I303" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28382,7 +28382,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC303" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD303" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -28408,10 +28408,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G304" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H304" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I304" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28474,7 +28474,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC304" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD304" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -28485,25 +28485,25 @@
         <x:v>vision_config/layer_23</x:v>
       </x:c>
       <x:c r="B305" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C305" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D305" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E305" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F305" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G305" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H305" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I305" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28566,10 +28566,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC305" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD305" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="24" hidden="0" customHeight="1">
@@ -28592,10 +28592,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G306" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H306" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I306" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28658,7 +28658,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC306" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD306" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -28684,10 +28684,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G307" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H307" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I307" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28750,7 +28750,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC307" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD307" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -28776,10 +28776,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G308" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H308" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I308" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28842,7 +28842,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC308" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD308" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -28868,10 +28868,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G309" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H309" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I309" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -28934,7 +28934,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC309" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD309" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -28960,10 +28960,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G310" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H310" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I310" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29026,7 +29026,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC310" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD310" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -29052,10 +29052,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G311" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H311" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I311" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29118,7 +29118,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC311" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD311" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -29144,10 +29144,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G312" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H312" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I312" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29210,7 +29210,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC312" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD312" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -29236,10 +29236,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G313" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H313" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I313" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29302,7 +29302,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC313" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD313" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -29328,10 +29328,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G314" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H314" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I314" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29394,7 +29394,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC314" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD314" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -29420,10 +29420,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G315" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H315" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I315" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29486,7 +29486,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC315" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD315" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -29512,10 +29512,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G316" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H316" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I316" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29578,7 +29578,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC316" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD316" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -29604,10 +29604,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G317" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H317" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I317" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29670,7 +29670,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC317" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD317" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -29681,25 +29681,25 @@
         <x:v>vision_config/layer_24</x:v>
       </x:c>
       <x:c r="B318" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C318" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D318" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E318" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F318" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G318" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H318" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I318" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29762,10 +29762,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC318" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD318" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="24" hidden="0" customHeight="1">
@@ -29788,10 +29788,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G319" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H319" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I319" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29854,7 +29854,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC319" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD319" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -29880,10 +29880,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G320" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H320" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I320" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -29946,7 +29946,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC320" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD320" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -29972,10 +29972,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G321" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H321" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I321" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30038,7 +30038,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC321" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD321" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -30064,10 +30064,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G322" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H322" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I322" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30130,7 +30130,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC322" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD322" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -30156,10 +30156,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G323" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H323" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I323" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30222,7 +30222,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC323" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD323" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -30248,10 +30248,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G324" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H324" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I324" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30314,7 +30314,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC324" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD324" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -30340,10 +30340,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G325" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H325" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I325" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30406,7 +30406,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC325" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD325" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -30432,10 +30432,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G326" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H326" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I326" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30498,7 +30498,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC326" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD326" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -30524,10 +30524,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G327" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H327" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I327" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30590,7 +30590,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC327" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD327" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -30616,10 +30616,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G328" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H328" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I328" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30682,7 +30682,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC328" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD328" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -30708,10 +30708,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G329" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H329" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I329" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30774,7 +30774,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC329" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD329" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -30800,10 +30800,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G330" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H330" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I330" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30866,7 +30866,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC330" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD330" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -30877,25 +30877,25 @@
         <x:v>vision_config/layer_25</x:v>
       </x:c>
       <x:c r="B331" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C331" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D331" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E331" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F331" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G331" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H331" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I331" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -30958,10 +30958,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC331" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD331" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="24" hidden="0" customHeight="1">
@@ -30984,10 +30984,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G332" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H332" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I332" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31050,7 +31050,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC332" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD332" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -31076,10 +31076,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G333" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H333" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I333" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31142,7 +31142,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC333" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD333" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -31168,10 +31168,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G334" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H334" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I334" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31234,7 +31234,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC334" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD334" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -31260,10 +31260,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G335" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H335" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I335" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31326,7 +31326,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC335" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD335" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -31352,10 +31352,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G336" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H336" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I336" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31418,7 +31418,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC336" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD336" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -31444,10 +31444,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G337" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H337" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I337" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31510,7 +31510,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC337" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD337" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -31536,10 +31536,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G338" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H338" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I338" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31602,7 +31602,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC338" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD338" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -31628,10 +31628,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G339" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H339" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I339" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31694,7 +31694,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC339" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD339" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -31720,10 +31720,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G340" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H340" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I340" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31786,7 +31786,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC340" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD340" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -31812,10 +31812,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G341" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H341" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I341" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31878,7 +31878,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC341" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD341" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -31904,10 +31904,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G342" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H342" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I342" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -31970,7 +31970,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC342" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD342" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -31996,10 +31996,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G343" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H343" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I343" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32062,7 +32062,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC343" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD343" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -32073,25 +32073,25 @@
         <x:v>vision_config/layer_26</x:v>
       </x:c>
       <x:c r="B344" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C344" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D344" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E344" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F344" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G344" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H344" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I344" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32154,10 +32154,10 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC344" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD344" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="24" hidden="0" customHeight="1">
@@ -32180,10 +32180,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G345" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H345" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I345" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32246,7 +32246,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC345" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD345" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -32272,10 +32272,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G346" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H346" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I346" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32338,7 +32338,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC346" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD346" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -32364,10 +32364,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G347" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H347" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I347" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32430,7 +32430,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC347" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD347" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -32456,10 +32456,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G348" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H348" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I348" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32522,7 +32522,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC348" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD348" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -32548,10 +32548,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G349" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H349" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I349" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32614,7 +32614,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC349" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD349" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -32640,10 +32640,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G350" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H350" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I350" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32706,7 +32706,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC350" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD350" s="12" t="str">
         <x:v>config.hidden_act=gelu_pytorch_tanh</x:v>
@@ -32732,10 +32732,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G351" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H351" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I351" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32798,7 +32798,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC351" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD351" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -32824,10 +32824,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G352" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H352" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I352" s="12" t="str">
         <x:v>config=未核验；激活/累加类型未核验</x:v>
@@ -32890,7 +32890,7 @@
         <x:v>https://huggingface.co/openbmb/MiniCPM-V-4.6/resolve/36f34a661a4bd35d0dc2294cb044d2584646c7d3/config.json</x:v>
       </x:c>
       <x:c r="AC352" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD352" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36665,7 +36665,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD393" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="394" ht="24" hidden="0" customHeight="1">
@@ -41173,7 +41173,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD442" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="443" ht="24" hidden="0" customHeight="1">
@@ -45681,7 +45681,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD491" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="492" ht="24" hidden="0" customHeight="1">
@@ -50189,7 +50189,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD540" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="541" ht="24" hidden="0" customHeight="1">
@@ -54697,7 +54697,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD589" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="590" ht="24" hidden="0" customHeight="1">
@@ -59205,7 +59205,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD638" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="639" ht="24" hidden="0" customHeight="1">
@@ -60743,7 +60743,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -61007,7 +61007,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -61020,7 +61023,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -61870,8 +61876,8 @@
       <x:c r="E88" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -61879,6 +61885,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
